--- a/assessment_forms/010_cardiorespiratory_fitness_assessment--assessment_forms.xlsx
+++ b/assessment_forms/010_cardiorespiratory_fitness_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -943,8 +943,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -972,12 +972,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'treadmill_(standard)',_'value':_'treadmill'}</t>
+          <t>treadmill_(standard)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Treadmill (Standard)', 'value': 'treadmill'}</t>
+          <t>Treadmill (Standard)</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'cycle_ergometer',_'value':_'cycle'}</t>
+          <t>cycle_ergometer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Cycle Ergometer', 'value': 'cycle'}</t>
+          <t>Cycle Ergometer</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'step_test',_'value':_'step_test'}</t>
+          <t>step_test</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Step Test', 'value': 'step_test'}</t>
+          <t>Step Test</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'1.5_mile_run',_'value':_'run'}</t>
+          <t>1.5_mile_run</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '1.5 Mile Run', 'value': 'run'}</t>
+          <t>1.5 Mile Run</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'elite',_'value':_'elite'}</t>
+          <t>elite</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Elite', 'value': 'elite'}</t>
+          <t>Elite</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'good',_'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Good', 'value': 'good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'average',_'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Average', 'value': 'average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fair',_'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fair', 'value': 'fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'poor',_'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Poor', 'value': 'poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
